--- a/inputs/Miscellaneous/A-Xtra_Storage.xlsx
+++ b/inputs/Miscellaneous/A-Xtra_Storage.xlsx
@@ -722,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -772,166 +772,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Fixed Horizon Parameters</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>LDS*, SDS*, BDS* (almacenamiento de larga duración, corta duración y baterías)</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>StorageLevelStart, OperationalLifeStorage</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>OSeMOSYS Global (base de datos abierta del modelo eléctrico mundial OSeMOSYS Global)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Nivel inicial de almacenamiento (0) y vida útil (larga duración 60 años, corta duración y baterías 30 años). Las baterías (BDS, solo Chile y Perú) copian los valores de corta duración.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>CapitalCostStorage</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>LDS* (almacenamiento de larga duración, 19 países)</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>CapitalCostStorage</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2023-2050</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>NREL ATB 2024 (Annual Technology Baseline del National Renewable Energy Laboratory, EE. UU.)</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Componente de energía del costo del almacenamiento: 20 833.33 millones de USD por PJ, equivalente a 75 USD por kWh, constante; cargado en la versión anterior del modelo ReLAC (agosto 2025). OSeMOSYS Global traía 52 694 millones de USD por PJ (≈ 190 USD/kWh), valor que no se usa. El componente de potencia está en la hoja Secondary Techs de A-O_Parametrization (PWRLDS*).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>CapitalCostStorage</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>SDS* (almacenamiento de corta duración, 19 países) y BDS* (baterías, Chile y Perú)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>CapitalCostStorage</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2023-2050</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>NREL ATB 2024 (Annual Technology Baseline del National Renewable Energy Laboratory, EE. UU.)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Componente de energía del costo: 32 777.77 millones de USD por PJ, equivalente a 118 USD por kWh, constante; cargado en la versión anterior del modelo ReLAC (agosto 2025). OSeMOSYS Global traía 42 051 millones de USD por PJ (≈ 151 USD/kWh), valor que no se usa. El componente de potencia (944 USD/kW) está en la hoja Secondary Techs de A-O_Parametrization (PWRSDS*, PWRBDS*).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>CapitalCostStorage</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>LDS*, SDS* (almacenamiento existente)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>ResidualStorageCapacity</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>2023-2050</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>OSeMOSYS Global (base de datos abierta del modelo eléctrico mundial OSeMOSYS Global)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Capacidad de almacenamiento existente; solo Argentina, Bolivia, Brasil, Haití y México tienen valores distintos de cero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>TechnologyStorage</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>PWRLDS* / PWRSDS* / PWRBDS* ↔ LDS* / SDS* / BDS* (vínculo entre la planta de almacenamiento y su depósito)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>TechnologyToStorage, TechnologyFromStorage</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>OSeMOSYS Global (base de datos abierta del modelo eléctrico mundial OSeMOSYS Global)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Indica qué tecnología carga (modo 1) y descarga (modo 2) cada depósito de almacenamiento.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/inputs/Miscellaneous/A-Xtra_Storage.xlsx
+++ b/inputs/Miscellaneous/A-Xtra_Storage.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Horizon Parameters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CapitalCostStorage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TechnologyStorage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fixed Horizon Parameters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CapitalCostStorage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TechnologyStorage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fuentes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fixed Horizon Parameters'!$A$1:$G$277</definedName>
@@ -736,7 +736,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Fuentes de los datos de este libro. Las fuentes SUBRAYADAS son supuestos propios del equipo de modelación (no provienen de una fuente externa). Hoja informativa: el modelo no la lee.</t>
+          <t>Fuentes de los datos de este libro. Las fuentes marcadas como 'Supuesto propio' son estimaciones internas del equipo de modelación (no provienen de una fuente externa). Hoja informativa: el modelo no la lee.</t>
         </is>
       </c>
     </row>

--- a/inputs/Miscellaneous/A-Xtra_Storage.xlsx
+++ b/inputs/Miscellaneous/A-Xtra_Storage.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Anios</t>
+          <t>Años</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
